--- a/Employee_Reports_wi52/Nhar Jaradal Cillo Q0494.xlsx
+++ b/Employee_Reports_wi52/Nhar Jaradal Cillo Q0494.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-321</v>
+        <v>-329</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-440</v>
+        <v>-448</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-680</v>
+        <v>-688</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-385</v>
+        <v>-393</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-385</v>
+        <v>-393</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-167</v>
+        <v>-175</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1538,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1587,11 +1587,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1624,11 +1624,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
